--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1681,7 +1681,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 04 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 05 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2648,11 +2648,11 @@
         <v>48</v>
       </c>
       <c r="B43" s="22" t="n">
-        <f aca="false">COUNTIFS(Income!$M$4:$M$503,"&gt;0",Income!$M$4:$M$503,"&lt;="&amp;OVERDUE_DAYS)</f>
+        <f aca="false">COUNTIFS(Income!$M$4:$M$503,"&gt;=0",Income!$M$4:$M$503,"&lt;="&amp;OVERDUE_DAYS)</f>
         <v>0</v>
       </c>
       <c r="C43" s="13" t="n">
-        <f aca="false">SUMIFS(Income!$I$4:$I$503,Income!$M$4:$M$503,"&gt;0",Income!$M$4:$M$503,"&lt;="&amp;OVERDUE_DAYS)</f>
+        <f aca="false">SUMIFS(Income!$I$4:$I$503,Income!$M$4:$M$503,"&gt;=0",Income!$M$4:$M$503,"&lt;="&amp;OVERDUE_DAYS)</f>
         <v>0</v>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1681,7 +1681,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 05 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 06 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3239,7 +3239,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="235">
   <si>
     <t xml:space="preserve">UAE Freelancer &amp; Small Business Bookkeeping Tracker 2026</t>
   </si>
@@ -648,7 +648,13 @@
     <t xml:space="preserve">Output VAT − recoverable input VAT.</t>
   </si>
   <si>
+    <t xml:space="preserve">CHECK — income in period not counted in any box above (must be 0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Non-recoverable VAT paid in period (cost to you)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK — expenses in period with an unrecognised VAT treatment (must be 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Registration check — taxable turnover, last 12 months to today</t>
@@ -968,7 +974,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1157,6 +1163,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1198,7 +1208,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1281,6 +1291,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDE9E7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1681,7 +1705,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 06 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 07 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3239,7 +3263,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>
@@ -21210,6 +21234,11 @@
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$J4="Paid"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G503">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>AND($G4&lt;&gt;"",ISNA(MATCH($G4,INDIRECT("Settings!$G$4:$G$7"),0)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -36867,6 +36896,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A3:N503"/>
+  <conditionalFormatting sqref="F4:F503">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>AND($F4&lt;&gt;"",ISNA(MATCH($F4,INDIRECT("Settings!$G$4:$G$7"),0)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:D503" type="list">
       <formula1>Settings!$F$4:$F$16</formula1>
@@ -37111,45 +37145,73 @@
         <v>200</v>
       </c>
     </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="47" t="n">
+        <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$P$4:$P$503,1)-C9-C10-C11-C12</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D18" s="47" t="n">
+        <v>202</v>
+      </c>
+      <c r="D18" s="48" t="n">
         <f aca="false">SUMIFS(Expenses!$G$4:$G$503,Expenses!$N$4:$N$503,1)-D14</f>
         <v>0</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="47" t="n">
+        <f aca="false">SUMIFS(Expenses!$E$4:$E$503,Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Standard 5%",Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Zero-rated 0%",Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Exempt",Expenses!$N$4:$N$503,1)-SUMIFS(Expenses!$E$4:$E$503,Expenses!$F$4:$F$503,"Out of scope",Expenses!$N$4:$N$503,1)</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D20" s="47" t="n">
+        <v>204</v>
+      </c>
+      <c r="D20" s="48" t="n">
         <f aca="true">SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Standard 5%",Income!$A$4:$A$503,"&gt;"&amp;(TODAY()-365))+SUMIFS(Income!$F$4:$F$503,Income!$G$4:$G$503,"Zero-rated 0%",Income!$A$4:$A$503,"&gt;"&amp;(TODAY()-365))</f>
         <v>24500</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D21" s="48" t="str">
+        <v>205</v>
+      </c>
+      <c r="D21" s="49" t="str">
         <f aca="false">IF(D20&gt;=VAT_MAND,"ABOVE MANDATORY THRESHOLD — must be registered",IF(D20&gt;=VAT_VOL,"Above voluntary threshold — may register","Below voluntary threshold"))</f>
         <v>Below voluntary threshold</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
+      <c r="B23" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B23:E23"/>
   </mergeCells>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="cellIs" priority="2" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" priority="3" operator="notEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -37175,149 +37237,149 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="50" t="str">
+        <v>212</v>
+      </c>
+      <c r="B4" s="51" t="str">
         <f aca="false">TEXT(FY_START,"dd-mmm-yyyy")&amp;" to "&amp;TEXT(EDATE(FY_START,12)-1,"dd-mmm-yyyy")</f>
         <v>01-Jan-2026 to 31-Dec-2026</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="51" t="n">
+        <v>214</v>
+      </c>
+      <c r="B5" s="52" t="n">
         <f aca="false">SUMIFS(Income!$F$4:$F$503,Income!$A$4:$A$503,"&gt;="&amp;FY_START,Income!$A$4:$A$503,"&lt;="&amp;EDATE(FY_START,12)-1)</f>
         <v>24500</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="B6" s="51" t="n">
+        <v>216</v>
+      </c>
+      <c r="B6" s="52" t="n">
         <f aca="false">SUMIFS(Expenses!$E$4:$E$503,Expenses!$L$4:$L$503,"Yes",Expenses!$A$4:$A$503,"&gt;="&amp;FY_START,Expenses!$A$4:$A$503,"&lt;="&amp;EDATE(FY_START,12)-1)</f>
         <v>11400</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" s="51" t="n">
+        <v>218</v>
+      </c>
+      <c r="B7" s="52" t="n">
         <f aca="false">SUMIFS(Expenses!$G$4:$G$503,Expenses!$L$4:$L$503,"Yes",Expenses!$H$4:$H$503,"No",Expenses!$A$4:$A$503,"&gt;="&amp;FY_START,Expenses!$A$4:$A$503,"&lt;="&amp;EDATE(FY_START,12)-1)</f>
         <v>0</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B8" s="52" t="n">
+        <v>220</v>
+      </c>
+      <c r="B8" s="53" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="51" t="n">
+        <v>222</v>
+      </c>
+      <c r="B9" s="52" t="n">
         <f aca="false">B5-B6-B7+B8</f>
         <v>13100</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="B10" s="50" t="str">
+        <v>224</v>
+      </c>
+      <c r="B10" s="51" t="str">
         <f aca="false">SBR_ELECT</f>
         <v>Yes</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="B11" s="50" t="str">
+        <v>225</v>
+      </c>
+      <c r="B11" s="51" t="str">
         <f aca="false">IF(AND(SBR_ELECT="Yes",B5&lt;=SBR_LIMIT,EDATE(FY_START,12)-1&lt;=SBR_END),"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" s="51" t="n">
+        <v>227</v>
+      </c>
+      <c r="B12" s="52" t="n">
         <f aca="false">MAX(0,B9-CT_BAND)</f>
         <v>0</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="53" t="n">
+        <v>229</v>
+      </c>
+      <c r="B13" s="54" t="n">
         <f aca="false">IF(B11="Yes",0,B12*CT_RATE)</f>
         <v>0</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="B14" s="54" t="n">
+        <v>231</v>
+      </c>
+      <c r="B14" s="55" t="n">
         <f aca="false">IF(B9&lt;=0,0,B13/B9)</f>
         <v>0</v>
       </c>
@@ -37325,22 +37387,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="B15" s="51" t="n">
+        <v>232</v>
+      </c>
+      <c r="B15" s="52" t="n">
         <f aca="false">B13/12</f>
         <v>0</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
+      <c r="A18" s="50" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1705,7 +1705,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 07 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 08 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3263,7 +3263,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1705,7 +1705,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 08 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 09 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3263,7 +3263,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1705,7 +1705,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 09 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 10 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3263,7 +3263,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">• VAT: 5% standard rate. Mandatory registration when taxable supplies exceed AED 375,000 in the past 12 months (or expected in the next 30 days); voluntary from AED 187,500.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Corporate Tax: 0% on taxable income up to AED 375,000, 9% above. Small Business Relief (elect if revenue ≤ AED 3,000,000) gives 0% for tax periods ending on or before 31 Dec 2026.</t>
+    <t xml:space="preserve">• Corporate Tax: 0% on taxable income up to AED 375,000, 9% above. Small Business Relief (elect if revenue ≤ AED 3,000,000) gives 0% for tax periods ending on or before 31 Dec 2029 — extended from 2026 by Ministerial Decision 131 of 2026 (issued 29 July 2026).</t>
   </si>
   <si>
     <t xml:space="preserve">• Registration deadlines and penalties are not modelled — this tracker estimates amounts, it does not file for you.</t>
@@ -342,7 +342,7 @@
     <t xml:space="preserve">Elect Small Business Relief? (Yes/No)</t>
   </si>
   <si>
-    <t xml:space="preserve">Available if revenue ≤ threshold below, for tax periods ending on or before 31 Dec 2026. Election is made in the CT return.</t>
+    <t xml:space="preserve">Available if revenue ≤ threshold below, for tax periods ending on or before 31 Dec 2029 (extended by Ministerial Decision 131 of 2026). Election is made in the CT return, every period — it is not automatic.</t>
   </si>
   <si>
     <t xml:space="preserve">Equipment &amp; hardware</t>
@@ -360,7 +360,7 @@
     <t xml:space="preserve">Small Business Relief last eligible period end</t>
   </si>
   <si>
-    <t xml:space="preserve">Relief not available for periods ending after this date.</t>
+    <t xml:space="preserve">Relief not available for periods ending after this date. Extended from 31 Dec 2026 to 31 Dec 2029 by Ministerial Decision 131 of 2026; checked 2026-09-10.</t>
   </si>
   <si>
     <t xml:space="preserve">Insurance</t>
@@ -2934,7 +2934,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
         <v>98</v>
       </c>
@@ -2963,12 +2963,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
         <v>104</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>46387</v>
+        <v>47483</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>105</v>

--- a/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
+++ b/products/uae-vat-tracker/UAE_Business_Bookkeeping_VAT_CT_Tracker_2026.xlsx
@@ -1705,7 +1705,7 @@
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="str">
         <f aca="true">"Financial year from "&amp;TEXT(FY_START,"dd mmm yyyy")&amp;"   ·   Today: "&amp;TEXT(TODAY(),"dd mmm yyyy")</f>
-        <v>Financial year from 01 Jan 2026   ·   Today: 10 Sep 2026</v>
+        <v>Financial year from 01 Jan 2026   ·   Today: 11 Sep 2026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3263,7 +3263,7 @@
       <c r="L5" s="38"/>
       <c r="M5" s="22" t="n">
         <f aca="true">IF(OR(A5="",J5="Paid",J5="Written off"),"",TODAY()-A5)</f>
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N5" s="22" t="str">
         <f aca="false">IF(M5="","",IF(M5&gt;OVERDUE_DAYS,"OVERDUE",""))</f>
